--- a/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>+0.63%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>-1.25%3960</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4010</v>
+        <v>3960</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.08%486</t>
+          <t>+1.03%491</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.08%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.88%640</t>
+          <t>+1.88%652</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.49%1980</t>
+          <t>-1.26%1955</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1980</v>
+        <v>1955</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.13%1840</t>
+          <t>+5.98%1950</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1840</v>
+        <v>1950</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.33%795</t>
+          <t>+2.39%814</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>+2.39%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.9%567</t>
+          <t>-8.29%520</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-8.29%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>567</v>
+        <v>520</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-7.69%1320</t>
+          <t>-3.41%1275</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>-3.41%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1320</v>
+        <v>1275</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.08%6175</t>
+          <t>-2.83%6000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6175</v>
+        <v>6000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>-6.31%4750</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-6.31%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5070</v>
+        <v>4750</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.3%4890</t>
+          <t>-2.04%4790</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4890</v>
+        <v>4790</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.22%9755</t>
+          <t>+0.56%9810</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9755</v>
+        <v>9810</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>-0.48%3130</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3145</v>
+        <v>3130</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:24</t>
+          <t>2026-10-27 22:41:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.14%826</t>
+          <t>-1.45%814</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.14%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.56%190</t>
+          <t>+0.26%190.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>190</v>
+        <v>190.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.04%255.5</t>
+          <t>-1.17%252.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>255.5</v>
+        <v>252.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.04%226.5</t>
+          <t>-3.75%218</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.04%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>226.5</v>
+        <v>218</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.59%777</t>
+          <t>-3.99%746</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.59%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>777</v>
+        <v>746</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.79%467</t>
+          <t>-0.21%466</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-7.34%581</t>
+          <t>-8.26%533</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-8.26%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>581</v>
+        <v>533</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.53%186</t>
+          <t>-0.81%184.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.53%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>186</v>
+        <v>184.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.01%201</t>
+          <t>+1%203</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>125.5</v>
+        <v>122.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.9%670</t>
+          <t>+2.54%687</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.39%654</t>
+          <t>-0.46%651</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.02%1560</t>
+          <t>-6.09%1465</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1560</v>
+        <v>1465</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.33%1420</t>
+          <t>-9.86%1280</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-9.86%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1420</v>
+        <v>1280</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.65%349</t>
+          <t>+2.44%357.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>349</v>
+        <v>357.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:25</t>
+          <t>2026-10-27 22:41:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.53%88.8</t>
+          <t>+0.79%89.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>88.8</v>
+        <v>89.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.06%16010</t>
+          <t>+0.03%16015</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>16010</v>
+        <v>16015</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-6.01%242.5</t>
+          <t>0%242.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.77%248</t>
+          <t>+2.62%254.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.77%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>248</v>
+        <v>254.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-4.19%594</t>
+          <t>-0.34%592</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-5.11%3065</t>
+          <t>-5.06%2910</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3065</v>
+        <v>2910</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.83%452</t>
+          <t>+0.44%454</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.83%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.54%403</t>
+          <t>-1.12%398.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>403</v>
+        <v>398.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.86%790</t>
+          <t>-4.68%753</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>790</v>
+        <v>753</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-5.19%201</t>
+          <t>-0.5%200</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.87%49.15</t>
+          <t>+1.53%49.9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>49.15</v>
+        <v>49.9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.93%597</t>
+          <t>-2.18%584</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.21%163</t>
+          <t>+1.84%166</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-6.32%118.5</t>
+          <t>-3.38%114.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-3.38%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>118.5</v>
+        <v>114.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-4.57%156.5</t>
+          <t>-2.24%153</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-2.24%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>156.5</v>
+        <v>153</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:26</t>
+          <t>2026-10-27 22:42:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.95%247</t>
+          <t>-0.2%246.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>247</v>
+        <v>246.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.54%72.4</t>
+          <t>+1.1%73.2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-5.79%114</t>
+          <t>-3.51%110</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.79%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.44%926</t>
+          <t>+1.08%936</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.28%1160</t>
+          <t>+2.59%1190</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+2.59%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1160</v>
+        <v>1190</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.55%45.25</t>
+          <t>+4.09%47.1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>45.25</v>
+        <v>47.1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>-2.04%7430</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7585</v>
+        <v>7430</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-4.05%2485</t>
+          <t>+1.21%2515</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2485</v>
+        <v>2515</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+1.85%165.5</t>
+          <t>+0.91%167</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>165.5</v>
+        <v>167</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-9.02%438.5</t>
+          <t>-4.1%420.5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-9.02%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>438.5</v>
+        <v>420.5</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-1.76%615</t>
+          <t>-4.88%585</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>615</v>
+        <v>585</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+2.99%55.2</t>
+          <t>-0.36%55</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+2.99%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:28</t>
+          <t>2026-10-27 22:42:02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0%158.5</t>
+          <t>+2.21%162</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.21%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>158.5</v>
+        <v>162</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:58</t>
+          <t>2026-10-27 22:54:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:41:59</t>
+          <t>2026-10-27 22:54:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:00</t>
+          <t>2026-10-27 22:54:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:02</t>
+          <t>2026-10-27 22:54:41</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:37</t>
+          <t>2026-10-27 23:22:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:38</t>
+          <t>2026-10-27 23:22:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:40</t>
+          <t>2026-10-27 23:22:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:41</t>
+          <t>2026-10-27 23:22:07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
